--- a/data/xlsx/bmet--cad-cam-design-and-cnc-machine-operation.xlsx
+++ b/data/xlsx/bmet--cad-cam-design-and-cnc-machine-operation.xlsx
@@ -649,7 +649,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -671,7 +673,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>10</v>
       </c>
@@ -693,7 +697,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -715,7 +721,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -737,7 +745,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>3</v>
       </c>
@@ -759,7 +769,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -781,7 +793,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -803,7 +817,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>4</v>
       </c>
@@ -825,7 +841,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -847,7 +865,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -869,7 +889,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -895,7 +917,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -917,7 +941,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>

--- a/data/xlsx/bmet--cad-cam-design-and-cnc-machine-operation.xlsx
+++ b/data/xlsx/bmet--cad-cam-design-and-cnc-machine-operation.xlsx
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -749,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
